--- a/Project_Up/backtest_results.xlsx
+++ b/Project_Up/backtest_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pick ₹</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>D+1 ₹</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>D+1 %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>D+1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>D+3 ₹</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>D+3 %</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>D+3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>D+5 ₹</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>D+5 %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>D+5</t>
         </is>
@@ -517,11 +505,15 @@
           <t>Gravita India Limited</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1825.8</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1825.8</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -561,11 +553,15 @@
           <t>Ajax Engineering Limited</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>579.1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>579.1</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -605,11 +601,15 @@
           <t>Gandhi Special Tubes Limited</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>903.1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>903.1</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -649,11 +649,15 @@
           <t>Metropolis Healthcare Limited</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>576.9</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>576.9</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -693,11 +697,15 @@
           <t>Axis Bank Limited</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1265</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -737,11 +745,15 @@
           <t>Adani Enterprises Limited</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3168.5</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3168.5</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -781,11 +793,15 @@
           <t>Anupam Rasayan India Limited</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1260.4</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1260.4</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -825,11 +841,15 @@
           <t>Sudarshan Chemical Industries Limited</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1252.8</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1252.8</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -869,11 +889,15 @@
           <t>Syrma Sgs Technology Limited</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1474.3</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1474.3</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -913,11 +937,15 @@
           <t>Tube Investments Of India Limited</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2870</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2870</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -957,11 +985,15 @@
           <t>Fsn E-Commerce Ventures Limited</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>338</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1001,11 +1033,15 @@
           <t>Jindal Poly Films Limited</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>637.55</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>637.55</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -1045,11 +1081,15 @@
           <t>Venky'S (India) Limited</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1575.6</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1575.6</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -1089,11 +1129,15 @@
           <t>Carraro India Limited</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>544.05</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>544.05</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -1133,11 +1177,15 @@
           <t>Anand Rathi Wealth Limited</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2182.9</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2182.9</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -1177,11 +1225,15 @@
           <t>Nuvama Wealth Management Limited</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1805</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -1221,11 +1273,15 @@
           <t>Arfin India Limited</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" t="n">
-        <v>85.40000000000001</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1265,11 +1321,15 @@
           <t>Asahi India Glass Limited</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" t="n">
-        <v>951.25</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>951.25</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1309,11 +1369,15 @@
           <t>Titan Company Limited</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5169.2</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5169.2</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1353,11 +1417,15 @@
           <t>Apcotex Industries Limited</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" t="n">
-        <v>625.25</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>625.25</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1396,42 +1464,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Hit Rate 1D</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Avg Return 1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Hit Rate 3D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Avg Return 3D</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Hit Rate 5D</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Avg Return 5D</t>
         </is>

--- a/Project_Up/backtest_results.xlsx
+++ b/Project_Up/backtest_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,50 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +77,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,1036 +480,1532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Pick ₹</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>D+1 ₹</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>D+1 %</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D+1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>D+3 ₹</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>D+3 %</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>D+3</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>D+5 ₹</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>D+5 %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>D+5</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>GRAVITA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Gravita India Limited</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1825.8</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>AJAXENGG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Ajax Engineering Limited</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>579.1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="F3" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>GANDHITUBE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Gandhi Special Tubes Limited</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>903.1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>METROPOLIS</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Metropolis Healthcare Limited</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>576.9</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="F5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Axis Bank Limited</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Adani Enterprises Limited</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>3168.5</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="F7" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>ANURAS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Anupam Rasayan India Limited</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1260.4</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="F8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>SUDARSCHEM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Sudarshan Chemical Industries Limited</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>1252.8</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="F9" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Syrma Sgs Technology Limited</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1474.3</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>TIINDIA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Tube Investments Of India Limited</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>2870</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="F11" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NYKAA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Fsn E-Commerce Ventures Limited</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>338</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>JINDALPOLY</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Jindal Poly Films Limited</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>637.55</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="F13" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>VENKEYS</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Venky'S (India) Limited</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1575.6</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>CARRARO</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Carraro India Limited</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>544.05</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="F15" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>ANANDRATHI</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Anand Rathi Wealth Limited</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2182.9</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>NUVAMA</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Nuvama Wealth Management Limited</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>1805</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="F17" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>ARFIN</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Arfin India Limited</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>85.4</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="F18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>ASAHIINDIA</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Asahi India Glass Limited</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>951.25</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="F19" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Titan Company Limited</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>5169.2</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="F20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>APCOTEXIND</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Apcotex Industries Limited</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>625.25</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="F21" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Grasim Industries Limited</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3258.0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>JYOTICNC</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Jyoti Cnc Automation Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>1029.8</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Bosch Limited</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>48780.0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Ge Vernova T&amp;D India Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>4339.2</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1462,164 +2024,174 @@
   </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate 1D</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Avg Return 1D</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate 3D</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Avg Return 3D</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate 5D</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Return 5D</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>All Picks</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Score ≥ 8</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Score 5–7</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Project_Up/backtest_results.xlsx
+++ b/Project_Up/backtest_results.xlsx
@@ -36,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -95,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -112,7 +117,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -480,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -488,7 +496,7 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
@@ -597,11 +605,13 @@
           <t>1825.8</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1800.2</t>
+        </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v/>
+        <v>-1.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -657,11 +667,13 @@
           <t>579.1</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>574.5</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.6</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
@@ -717,11 +729,13 @@
           <t>903.1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>900.95</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -777,11 +791,13 @@
           <t>576.9</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
-        <v/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>582.35</t>
+        </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v/>
+        <v>-1.04</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -837,11 +853,13 @@
           <t>1265</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.77</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -897,11 +915,13 @@
           <t>3168.5</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
-        <v/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2859.1</t>
+        </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v/>
+        <v>-9.76</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -957,11 +977,13 @@
           <t>1260.4</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1262.8</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.19</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1017,11 +1039,13 @@
           <t>1252.8</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1266.8</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.79</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1077,11 +1101,13 @@
           <t>1474.3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1437.0</t>
+        </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v/>
+        <v>-2.53</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1137,11 +1163,13 @@
           <t>2870</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
-        <v/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2780.0</t>
+        </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v/>
+        <v>-2.11</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1197,11 +1225,13 @@
           <t>338</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>349.55</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4.14</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1257,11 +1287,13 @@
           <t>637.55</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
-        <v/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>631.35</t>
+        </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v/>
+        <v>-0.71</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1367,7 +1399,7 @@
           <t>Carraro India Limited</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1377,11 +1409,13 @@
           <t>544.05</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>559.4</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.29</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1427,7 +1461,7 @@
           <t>Anand Rathi Wealth Limited</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1487,7 +1521,7 @@
           <t>Nuvama Wealth Management Limited</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1497,11 +1531,13 @@
           <t>1805</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>1753.6</t>
+        </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v/>
+        <v>-2.85</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1547,7 +1583,7 @@
           <t>Arfin India Limited</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1557,11 +1593,13 @@
           <t>85.4</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>87.23</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.7</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1645,7 @@
           <t>Asahi India Glass Limited</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1617,11 +1655,13 @@
           <t>951.25</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n">
-        <v/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>952.05</t>
+        </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v/>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1667,7 +1707,7 @@
           <t>Titan Company Limited</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1677,11 +1717,13 @@
           <t>5169.2</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5102.4</t>
+        </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v/>
+        <v>-1.29</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1727,7 +1769,7 @@
           <t>Apcotex Industries Limited</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1737,11 +1779,13 @@
           <t>625.25</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>646.3</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>3.37</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1787,7 +1831,7 @@
           <t>Grasim Industries Limited</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1797,11 +1841,13 @@
           <t>3258.0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3371.0</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>2.46</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1847,7 +1893,7 @@
           <t>Jyoti Cnc Automation Limited</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1907,7 +1953,7 @@
           <t>Bosch Limited</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1967,7 +2013,7 @@
           <t>Ge Vernova T&amp;D India Limited</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2009,6 +2055,1142 @@
         <is>
           <t>—</t>
         </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>301.7</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>305.7</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>ETHOSLTD</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Ethos Limited</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2898.7</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CEIGALL</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Ceigall India Limited</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>341.35</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Navin Fluorine International Limited</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>8675.5</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Motilal Oswal Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1042.9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>1974.9</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Emudhra Limited</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>547.85</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>IRISDOREME</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Iris Clothings Limited</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>58.48</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>AXISCADES</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Axiscades Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1671.2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>5066.0</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ABSLAMC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Birla Sun Life Amc Limited</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1051.8</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Indian Bank</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>898.75</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Axis Bank Limited</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Bharat Electronics Limited</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>414.45</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Bosch Limited</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Indus Towers Limited</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>388.8</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FINEORG</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Fine Organic Industries Limited</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>5282.8</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Dlf Limited</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>691.05</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ARFIN</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Arfin India Limited</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>87.23</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>GANDHITUBE</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Gandhi Special Tubes Limited</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>900.95</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Sbc Exports Limited</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>42.15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2084,16 +3266,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2124,16 +3306,16 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -2164,16 +3346,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">

--- a/Project_Up/backtest_results.xlsx
+++ b/Project_Up/backtest_results.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -496,15 +496,17 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -578,6 +580,16 @@
           <t>D+5</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>D+7 ₹</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>D+7 %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -618,27 +630,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>1749.1</t>
+        </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v/>
+        <v>-4.2</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
-        <v/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>1661.6</t>
+        </is>
       </c>
       <c r="M2" s="4" t="n">
-        <v/>
+        <v>-8.99</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -680,27 +702,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
-        <v/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>570.65</t>
+        </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v/>
+        <v>-0.08</v>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>582.45</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>1.99</v>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -742,27 +774,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>896.4</t>
+        </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v/>
+        <v>-0.21</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>900.15</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>0.21</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -804,27 +846,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
-        <v/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>582.2</t>
+        </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v/>
+        <v>-1.06</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>588.7</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>0.04</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -866,27 +918,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1253.9</t>
+        </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v/>
+        <v>-0.88</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1273.0</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0.63</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -928,27 +990,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
-        <v/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>2891.8</t>
+        </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v/>
+        <v>-8.73</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
-        <v/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>2938.0</t>
+        </is>
       </c>
       <c r="M7" s="4" t="n">
-        <v/>
+        <v>-7.27</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -990,27 +1062,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1240.3</t>
+        </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v/>
+        <v>-1.59</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n">
-        <v/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1238.7</t>
+        </is>
       </c>
       <c r="M8" s="4" t="n">
-        <v/>
+        <v>-1.72</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1052,27 +1134,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
-        <v/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>1245.8</t>
+        </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v/>
+        <v>-0.88</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
-        <v/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>1222.8</t>
+        </is>
       </c>
       <c r="M9" s="4" t="n">
-        <v/>
+        <v>-2.71</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1114,27 +1206,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1434.0</t>
+        </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v/>
+        <v>-2.73</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
-        <v/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1457.3</t>
+        </is>
       </c>
       <c r="M10" s="4" t="n">
-        <v/>
+        <v>-1.15</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1176,27 +1278,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
-        <v/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>2720.0</t>
+        </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v/>
+        <v>-4.23</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
-        <v/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>2698.0</t>
+        </is>
       </c>
       <c r="M11" s="4" t="n">
-        <v/>
+        <v>-5</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1238,27 +1350,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v/>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>337.4</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.52</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n">
-        <v/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>332.5</t>
+        </is>
       </c>
       <c r="M12" s="4" t="n">
-        <v/>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1300,27 +1422,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>686.25</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>7.93</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>672.35</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>5.74</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1382,6 +1514,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="O14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1411,7 +1549,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>559.4</t>
+          <t>552.43</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
@@ -1422,27 +1560,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
-        <v/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>535.25</t>
+        </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v/>
+        <v>-2.83</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
-        <v/>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>533.65</t>
+        </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v/>
+        <v>-3.12</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1504,6 +1652,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="O16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1544,27 +1698,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>1841.0</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>1.99</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v/>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>1815.6</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0.59</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1606,27 +1770,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v/>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>87.87</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>2.45</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L18" s="2" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>87.24</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>1.71</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1668,27 +1842,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
-        <v/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>951.05</t>
+        </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v/>
+        <v>-0.17</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>955.9</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0.34</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1730,27 +1914,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5074.0</t>
+        </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v/>
+        <v>-1.84</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n">
-        <v/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5020.0</t>
+        </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v/>
+        <v>-2.89</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1792,27 +1986,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>628.65</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.54</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>635.5</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>1.64</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1854,27 +2058,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v/>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3294.9</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.15</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L22" s="2" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3322.0</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.97</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1936,6 +2150,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="O23" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1996,6 +2216,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="O24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2056,6 +2282,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="O25" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2085,7 +2317,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>305.7</t>
+          <t>303.62</t>
         </is>
       </c>
       <c r="G26" s="6" t="n">
@@ -2094,22 +2326,32 @@
       <c r="H26" s="2" t="n">
         <v/>
       </c>
-      <c r="I26" s="2" t="n">
-        <v/>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>418.25</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>39.58</v>
       </c>
       <c r="K26" s="2" t="n">
         <v/>
       </c>
-      <c r="L26" s="2" t="n">
-        <v/>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>480.85</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>60.47</v>
       </c>
       <c r="N26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P26" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2139,20 +2381,24 @@
           <t>2898.7</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n">
-        <v/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2879.4</t>
+        </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v/>
+        <v>-0.67</v>
       </c>
       <c r="H27" s="5" t="n">
         <v/>
       </c>
-      <c r="I27" s="5" t="n">
-        <v/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>2793.1</t>
+        </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v/>
+        <v>-3.64</v>
       </c>
       <c r="K27" s="5" t="n">
         <v/>
@@ -2164,6 +2410,12 @@
         <v/>
       </c>
       <c r="N27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P27" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2193,20 +2445,24 @@
           <t>341.35</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>344.7</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.98</v>
       </c>
       <c r="H28" s="2" t="n">
         <v/>
       </c>
-      <c r="I28" s="2" t="n">
-        <v/>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>347.55</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>1.82</v>
       </c>
       <c r="K28" s="2" t="n">
         <v/>
@@ -2218,6 +2474,12 @@
         <v/>
       </c>
       <c r="N28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P28" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2247,20 +2509,24 @@
           <t>8675.5</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n">
-        <v/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>8636.0</t>
+        </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v/>
+        <v>-0.46</v>
       </c>
       <c r="H29" s="5" t="n">
         <v/>
       </c>
-      <c r="I29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>8697.0</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.25</v>
       </c>
       <c r="K29" s="5" t="n">
         <v/>
@@ -2272,6 +2538,12 @@
         <v/>
       </c>
       <c r="N29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P29" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2328,6 +2600,12 @@
       <c r="N30" s="2" t="n">
         <v/>
       </c>
+      <c r="O30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2382,6 +2660,12 @@
       <c r="N31" s="5" t="n">
         <v/>
       </c>
+      <c r="O31" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2436,6 +2720,12 @@
       <c r="N32" s="2" t="n">
         <v/>
       </c>
+      <c r="O32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2490,6 +2780,12 @@
       <c r="N33" s="5" t="n">
         <v/>
       </c>
+      <c r="O33" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2544,6 +2840,12 @@
       <c r="N34" s="2" t="n">
         <v/>
       </c>
+      <c r="O34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2571,20 +2873,24 @@
           <t>5066.0</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>4965.5</t>
+        </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v/>
+        <v>-1.98</v>
       </c>
       <c r="H35" s="5" t="n">
         <v/>
       </c>
-      <c r="I35" s="5" t="n">
-        <v/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>4905.5</t>
+        </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v/>
+        <v>-3.17</v>
       </c>
       <c r="K35" s="5" t="n">
         <v/>
@@ -2596,6 +2902,12 @@
         <v/>
       </c>
       <c r="N35" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P35" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2625,20 +2937,24 @@
           <t>1051.8</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
-        <v/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1029.1</t>
+        </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v/>
+        <v>-2.16</v>
       </c>
       <c r="H36" s="2" t="n">
         <v/>
       </c>
-      <c r="I36" s="2" t="n">
-        <v/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>1045.2</t>
+        </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v/>
+        <v>-0.63</v>
       </c>
       <c r="K36" s="2" t="n">
         <v/>
@@ -2650,6 +2966,12 @@
         <v/>
       </c>
       <c r="N36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P36" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2679,20 +3001,24 @@
           <t>898.75</t>
         </is>
       </c>
-      <c r="F37" s="5" t="n">
-        <v/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>881.75</t>
+        </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v/>
+        <v>-1.89</v>
       </c>
       <c r="H37" s="5" t="n">
         <v/>
       </c>
-      <c r="I37" s="5" t="n">
-        <v/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>888.75</t>
+        </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v/>
+        <v>-1.11</v>
       </c>
       <c r="K37" s="5" t="n">
         <v/>
@@ -2704,6 +3030,12 @@
         <v/>
       </c>
       <c r="N37" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P37" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2733,20 +3065,24 @@
           <t>1300.0</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
-        <v/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1258.0</t>
+        </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v/>
+        <v>-3.23</v>
       </c>
       <c r="H38" s="2" t="n">
         <v/>
       </c>
-      <c r="I38" s="2" t="n">
-        <v/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>1267.0</t>
+        </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v/>
+        <v>-2.54</v>
       </c>
       <c r="K38" s="2" t="n">
         <v/>
@@ -2758,6 +3094,12 @@
         <v/>
       </c>
       <c r="N38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P38" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2787,20 +3129,24 @@
           <t>414.45</t>
         </is>
       </c>
-      <c r="F39" s="5" t="n">
-        <v/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>411.2</t>
+        </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v/>
+        <v>-0.78</v>
       </c>
       <c r="H39" s="5" t="n">
         <v/>
       </c>
-      <c r="I39" s="5" t="n">
-        <v/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>408.6</t>
+        </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v/>
+        <v>-1.41</v>
       </c>
       <c r="K39" s="5" t="n">
         <v/>
@@ -2812,6 +3158,12 @@
         <v/>
       </c>
       <c r="N39" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P39" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2868,6 +3220,12 @@
       <c r="N40" s="2" t="n">
         <v/>
       </c>
+      <c r="O40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2922,6 +3280,12 @@
       <c r="N41" s="5" t="n">
         <v/>
       </c>
+      <c r="O41" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2949,20 +3313,24 @@
           <t>5282.8</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
-        <v/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>5255.5</t>
+        </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v/>
+        <v>-0.52</v>
       </c>
       <c r="H42" s="2" t="n">
         <v/>
       </c>
-      <c r="I42" s="2" t="n">
-        <v/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>5179.5</t>
+        </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v/>
+        <v>-1.96</v>
       </c>
       <c r="K42" s="2" t="n">
         <v/>
@@ -2974,6 +3342,12 @@
         <v/>
       </c>
       <c r="N42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P42" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -3003,20 +3377,24 @@
           <t>691.05</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>675.15</t>
+        </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v/>
+        <v>-2.3</v>
       </c>
       <c r="H43" s="5" t="n">
         <v/>
       </c>
-      <c r="I43" s="5" t="n">
-        <v/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>681.65</t>
+        </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v/>
+        <v>-1.36</v>
       </c>
       <c r="K43" s="5" t="n">
         <v/>
@@ -3028,6 +3406,12 @@
         <v/>
       </c>
       <c r="N43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P43" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -3057,20 +3441,24 @@
           <t>87.23</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
-        <v/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v/>
+        <v>-1.98</v>
       </c>
       <c r="H44" s="2" t="n">
         <v/>
       </c>
-      <c r="I44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>89.09</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>2.13</v>
       </c>
       <c r="K44" s="2" t="n">
         <v/>
@@ -3082,6 +3470,12 @@
         <v/>
       </c>
       <c r="N44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P44" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -3111,20 +3505,24 @@
           <t>900.95</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>896.6</t>
+        </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v/>
+        <v>-0.48</v>
       </c>
       <c r="H45" s="5" t="n">
         <v/>
       </c>
-      <c r="I45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>902.55</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>0.18</v>
       </c>
       <c r="K45" s="5" t="n">
         <v/>
@@ -3136,6 +3534,12 @@
         <v/>
       </c>
       <c r="N45" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P45" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -3165,20 +3569,24 @@
           <t>42.15</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
-        <v/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>42.04</t>
+        </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v/>
+        <v>-0.26</v>
       </c>
       <c r="H46" s="2" t="n">
         <v/>
       </c>
-      <c r="I46" s="2" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>43.25</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>2.61</v>
       </c>
       <c r="K46" s="2" t="n">
         <v/>
@@ -3190,6 +3598,3260 @@
         <v/>
       </c>
       <c r="N46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>TATACAP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Tata Capital Limited</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>367.9</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>367.85</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>371.85</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1984.8</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1929.0</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>1916.0</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Ajax Engineering Limited</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>574.5</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>573.95</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>579.75</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Solar Industries India Limited</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>20108.0</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>20060.0</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>21500.0</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>AGARWALEYE</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Agarwal'S Health Care Limited</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>513.2</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>508.7</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>511.45</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>GARFIBRES</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Garware Technical Fibres Limited</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>812.85</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>842.7</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>800.05</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Bharat Forge Limited</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>2104.9</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>2052.2</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>1981.0</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>POLYPLEX</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Polyplex Corporation Limited</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1202.7</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1191.0</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Krishival Foods Limited</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>413.5</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>416.3</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Piramal Pharma Limited</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>214.49</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>214.22</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Oil India Limited</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>489.0</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>488.3</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>METROPOLIS</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Metropolis Healthcare Limited</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>591.9</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>588.7</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>SMCGLOBAL</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Smc Global Securities Limited</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>79.42</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>81.25</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>USHAMART</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Usha Martin Limited</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>515.65</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>514.15</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Elgi Equipments Limited</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>630.35</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>642.1</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N61" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O61" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Data Patterns (India) Limited</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>4587.3</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>4585.0</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>JINDRILL</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Jindal Drilling And Industries Limited</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>649.9</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>663.05</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Zydus Wellness Limited</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>538.2</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>531.7</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Arvind Limited</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>562.5</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>552.95</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>COSMOFIRST</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Cosmo First Limited</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>940.15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>919.85</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M66" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Rossell Techsys Limited</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>1116.3</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>1150.5</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M67" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N67" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>PRINCEPIPE</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Prince Pipes And Fittings Limited</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>289.5</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>283.0</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>GANDHITUBE</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Gandhi Special Tubes Limited</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>902.55</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>900.15</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O69" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>RML</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Rane (Madras) Limited</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1127.4</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1295.9</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Eternal Limited</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>324.8</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>322.75</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O71" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>STAR</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Strides Pharma Science Limited</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1053.6</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1059.6</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>SPLPETRO</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Supreme Petrochem Limited</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>725.8</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>771.05</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M73" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N73" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O73" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>HARSHA</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Harsha Engineers International Limited</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>454.35</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Oil India Limited</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>488.3</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J75" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M75" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O75" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P75" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Amber Enterprises India Limited</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>7474.0</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Panama Petrochem Limited</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>495.45</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J77" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N77" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>GANDHITUBE</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Gandhi Special Tubes Limited</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>900.15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>JSWDULUX</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Jsw Dulux Limited</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>3174.5</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N79" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Krishival Foods Limited</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>416.3</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>GANDHAR</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Gandhar Oil Refinery (India) Limited</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>267.6</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M81" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N81" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Limited</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>601.0</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>THEJO</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Thejo Engineering Limited</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>2125.3</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N83" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O83" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Nazara Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>368.65</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>POLYPLEX</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Polyplex Corporation Limited</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>1191.0</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M85" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O85" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SPAL</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>S. P. Apparels Limited</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1071.1</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>STAR</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Strides Pharma Science Limited</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>1059.6</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M87" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O87" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>INDIGOPNTS</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Indigo Paints Limited</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1185.8</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M88" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>RISHABH</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Rishabh Instruments Limited</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>738.45</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J89" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M89" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N89" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O89" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P89" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>KINGFA</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Kingfa Science &amp; Technology (India) Limited</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>5932.5</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>TCPLPACK</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Tcpl Packaging Limited</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>4091.9</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M91" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O91" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P91" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>AARTIPHARM</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Aarti Pharmalabs Limited</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>858.8</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M92" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P92" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Limited</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>690.6</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M93" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P93" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Arvind Limited</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>562.5</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M94" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P94" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>SMCGLOBAL</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Smc Global Securities Limited</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>79.42</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M95" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N95" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P95" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ARFIN</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Arfin India Limited</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>89.09</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M96" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P96" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>METROPOLIS</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Metropolis Healthcare Limited</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>591.9</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J97" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M97" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O97" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P97" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ABSLAMC</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Birla Sun Life Amc Limited</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1045.2</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M98" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="P98" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>COSMOFIRST</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Cosmo First Limited</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>940.15</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v/>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v/>
+      </c>
+      <c r="J99" s="4" t="n">
+        <v/>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v/>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M99" s="4" t="n">
+        <v/>
+      </c>
+      <c r="N99" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O99" s="5" t="n">
+        <v/>
+      </c>
+      <c r="P99" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -3204,7 +6866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3215,6 +6877,8 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3258,6 +6922,16 @@
           <t>Avg Return 5D</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Hit Rate 7D</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Return 7D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3266,34 +6940,44 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>55.0%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3306,34 +6990,44 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>-1.60%</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3346,34 +7040,44 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7.46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
